--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Proyectos/cursos_activos/inserta_once/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UsuarioM\Downloads\big_data\bloques\matematicas\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54222956-CA8B-9540-87B0-F23EEB278FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9D44ED-F1E7-4493-9957-761FA41B6BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="740" windowWidth="38080" windowHeight="19940" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,14 @@
     <sheet name="3_Satisfaccion" sheetId="4" r:id="rId4"/>
     <sheet name="4_Probabilidad" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$4</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'1_Precios'!$B$4</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="157">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -487,6 +495,27 @@
   </si>
   <si>
     <t>Dashboard 4: Probabilidad y Frecuencias (Canales)</t>
+  </si>
+  <si>
+    <t>Conclusiones:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media y mediana no son parecidas y esto implica muchos outliners, que distorsiona la media </t>
+  </si>
+  <si>
+    <t>Se venden muchos productos en el rango de precios entre 6 y 70</t>
+  </si>
+  <si>
+    <t>la desviacion tipica eas muy alta porque hay mucha diferencia entre la media y la mediana</t>
+  </si>
+  <si>
+    <t>el ticket medio de nuestra tienda es 35.</t>
+  </si>
+  <si>
+    <t>18 euros es el precio que mas se repite</t>
+  </si>
+  <si>
+    <t>en este caso, el mejor indicador es la mediana debido a que la distancia entre la media y la mediana es muy alta</t>
   </si>
 </sst>
 </file>
@@ -628,6 +657,680 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{495CFF4B-DF7B-4A79-B85A-CF110FAEB0C6}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>Precio_Unitario</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F90F2B4F-971C-2F5E-5BA2-7CE38FAB3CCE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11628120" y="2000250"/>
+              <a:ext cx="5905500" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-ES" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -918,9 +1621,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -964,7 +1667,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1008,7 +1711,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1052,7 +1755,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1096,7 +1799,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1140,7 +1843,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -1184,7 +1887,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -1228,7 +1931,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -1272,7 +1975,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -1316,7 +2019,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1360,7 +2063,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -1404,7 +2107,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1011</v>
       </c>
@@ -1448,7 +2151,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1012</v>
       </c>
@@ -1492,7 +2195,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1013</v>
       </c>
@@ -1536,7 +2239,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1014</v>
       </c>
@@ -1580,7 +2283,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1015</v>
       </c>
@@ -1624,7 +2327,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1016</v>
       </c>
@@ -1668,7 +2371,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1017</v>
       </c>
@@ -1712,7 +2415,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1018</v>
       </c>
@@ -1756,7 +2459,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1019</v>
       </c>
@@ -1800,7 +2503,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1020</v>
       </c>
@@ -1844,7 +2547,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1021</v>
       </c>
@@ -1888,7 +2591,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1022</v>
       </c>
@@ -1932,7 +2635,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1023</v>
       </c>
@@ -1976,7 +2679,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1024</v>
       </c>
@@ -2020,7 +2723,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1025</v>
       </c>
@@ -2064,7 +2767,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1026</v>
       </c>
@@ -2108,7 +2811,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1027</v>
       </c>
@@ -2152,7 +2855,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1028</v>
       </c>
@@ -2196,7 +2899,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1029</v>
       </c>
@@ -2240,7 +2943,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1030</v>
       </c>
@@ -2284,7 +2987,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1031</v>
       </c>
@@ -2328,7 +3031,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1032</v>
       </c>
@@ -2372,7 +3075,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1033</v>
       </c>
@@ -2416,7 +3119,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1034</v>
       </c>
@@ -2460,7 +3163,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1035</v>
       </c>
@@ -2504,7 +3207,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1036</v>
       </c>
@@ -2548,7 +3251,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1037</v>
       </c>
@@ -2592,7 +3295,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1038</v>
       </c>
@@ -2636,7 +3339,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1039</v>
       </c>
@@ -2680,7 +3383,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1040</v>
       </c>
@@ -2724,7 +3427,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1041</v>
       </c>
@@ -2768,7 +3471,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1042</v>
       </c>
@@ -2820,20 +3523,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="93.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -2847,7 +3550,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -2857,9 +3560,12 @@
       <c r="D5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="4">
+        <f>AVERAGE(B:B)</f>
+        <v>60.011904761904759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2869,9 +3575,12 @@
       <c r="D6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="4">
+        <f>MEDIAN(B:B)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -2881,9 +3590,12 @@
       <c r="D7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" s="4">
+        <f>_xlfn.MODE.SNGL(B:B)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -2893,9 +3605,12 @@
       <c r="D8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="4">
+        <f>_xlfn.STDEV.S(B:B)</f>
+        <v>63.23692269082472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -2903,7 +3618,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -2911,7 +3626,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2922,7 +3637,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -2930,7 +3645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -2938,7 +3653,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -2946,7 +3661,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2954,7 +3669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -2962,7 +3677,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -2970,7 +3685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -2978,7 +3693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -2986,7 +3701,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -2994,7 +3709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3002,7 +3717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3010,7 +3725,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3018,7 +3733,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3026,7 +3741,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3034,7 +3749,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3042,7 +3757,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3050,7 +3765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3058,7 +3773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -3066,55 +3781,76 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
       <c r="B31">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
       <c r="B32">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
       <c r="B33">
         <v>25</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
       <c r="B34">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
       <c r="B35">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3122,7 +3858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3130,7 +3866,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3138,7 +3874,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3146,7 +3882,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3154,7 +3890,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3162,7 +3898,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3170,7 +3906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3178,7 +3914,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3186,7 +3922,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3194,7 +3930,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3204,13 +3940,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -3218,12 +3955,12 @@
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3240,7 +3977,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3255,7 +3992,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3270,7 +4007,7 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3285,7 +4022,7 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3300,7 +4037,7 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -3311,7 +4048,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -3322,7 +4059,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3336,7 +4073,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -3347,7 +4084,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3358,7 +4095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3369,7 +4106,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3380,7 +4117,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3391,7 +4128,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -3402,7 +4139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3413,7 +4150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3424,7 +4161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -3435,7 +4172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3446,7 +4183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3457,7 +4194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3468,7 +4205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3479,7 +4216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3490,7 +4227,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3501,7 +4238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3512,7 +4249,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3523,7 +4260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -3534,7 +4271,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -3545,7 +4282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -3556,7 +4293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -3567,7 +4304,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -3578,7 +4315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3589,7 +4326,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -3600,7 +4337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3611,7 +4348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3622,7 +4359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3633,7 +4370,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3644,7 +4381,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3655,7 +4392,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3666,7 +4403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3677,7 +4414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3688,7 +4425,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3699,7 +4436,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3710,7 +4447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3729,7 +4466,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -3737,12 +4474,12 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3756,7 +4493,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3768,7 +4505,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3780,7 +4517,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3792,7 +4529,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3800,7 +4537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -3808,7 +4545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -3819,7 +4556,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3833,7 +4570,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -3845,7 +4582,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3857,7 +4594,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3869,7 +4606,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3881,7 +4618,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3893,7 +4630,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -3901,7 +4638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3909,7 +4646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3920,7 +4657,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -3928,7 +4665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3936,7 +4673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3944,7 +4681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3952,7 +4689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3960,7 +4697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3968,7 +4705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3976,7 +4713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3984,7 +4721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3992,7 +4729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4000,7 +4737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4008,7 +4745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4016,7 +4753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4024,7 +4761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4032,7 +4769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4040,7 +4777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -4048,7 +4785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -4056,7 +4793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -4064,7 +4801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -4072,7 +4809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -4080,7 +4817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -4088,7 +4825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4096,7 +4833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4104,7 +4841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4112,7 +4849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -4120,7 +4857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4128,7 +4865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -4144,25 +4881,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98BB36B-BB56-6748-8634-193EA745B178}">
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -4170,7 +4907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -4190,7 +4927,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -4204,7 +4941,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -4218,7 +4955,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -4232,7 +4969,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -4246,7 +4983,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -4254,7 +4991,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -4265,7 +5002,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -4276,7 +5013,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4287,7 +5024,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -4295,7 +5032,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4306,7 +5043,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -4314,7 +5051,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -4325,7 +5062,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -4333,7 +5070,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -4341,7 +5078,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -4349,7 +5086,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -4357,7 +5094,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -4365,7 +5102,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -4373,7 +5110,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4381,7 +5118,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -4389,7 +5126,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -4397,7 +5134,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -4405,7 +5142,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4413,7 +5150,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4421,7 +5158,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4429,7 +5166,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4437,7 +5174,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4445,7 +5182,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4453,7 +5190,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4461,7 +5198,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -4469,7 +5206,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -4477,7 +5214,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -4485,7 +5222,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -4493,7 +5230,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -4501,7 +5238,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -4509,7 +5246,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4517,7 +5254,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4525,7 +5262,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4533,7 +5270,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -4541,7 +5278,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4549,7 +5286,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UsuarioM\Downloads\big_data\bloques\matematicas\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9D44ED-F1E7-4493-9957-761FA41B6BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72E596-1F4E-4C05-98C4-D6DAD5B88FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$4</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'1_Precios'!$B$4</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="161">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -516,6 +513,18 @@
   </si>
   <si>
     <t>en este caso, el mejor indicador es la mediana debido a que la distancia entre la media y la mediana es muy alta</t>
+  </si>
+  <si>
+    <t>la tendencia deberia ser entre 50 y 100 ya que tiene un mayor beneficio.</t>
+  </si>
+  <si>
+    <t>la desviacion tipica de estos valores es baja. La concentracion spobre los beneficios esta entre 0 y 50.</t>
+  </si>
+  <si>
+    <t>como la desviacion tipica es cercana a 0, la concentración de ventas de los productos es mayor.</t>
+  </si>
+  <si>
+    <t>vende el grueso de sus productos con un margen de beneficios pequeño. Entre unos 20 y 30 euros de beneficio.</t>
   </si>
 </sst>
 </file>
@@ -659,6 +668,574 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Dispersión coste vs beneficio</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2_Beneficios'!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beneficio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'2_Beneficios'!$B$5:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2_Beneficios'!$C$5:$C$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2E12-4F94-AF0D-D9510D6FC336}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="835672128"/>
+        <c:axId val="835671648"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="835672128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="835671648"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="835671648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="835672128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -703,6 +1280,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1250,6 +1867,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1299,7 +2432,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11628120" y="2000250"/>
+              <a:off x="12694920" y="2000250"/>
               <a:ext cx="5905500" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1328,6 +2461,47 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6484620</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3246120</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{311C651B-C93D-291E-D181-64AE538CE65D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3946,21 +5120,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="94.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="79.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3977,7 +5152,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3990,9 +5165,12 @@
       <c r="E5" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F5" s="4">
+        <f>AVERAGE(C:C)</f>
+        <v>32.511904761904759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -4005,9 +5183,15 @@
       <c r="E6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="4">
+        <f>_xlfn.STDEV.S(C:C)</f>
+        <v>20.550499399082351</v>
+      </c>
+      <c r="H6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -4020,9 +5204,12 @@
       <c r="E7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="4">
+        <f>MIN(C:C)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -4035,9 +5222,12 @@
       <c r="E8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="4">
+        <f>MAX(C:C)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -4048,7 +5238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -4059,7 +5249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -4073,7 +5263,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -4084,7 +5274,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4094,8 +5284,11 @@
       <c r="C13">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -4105,8 +5298,11 @@
       <c r="C14">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4116,8 +5312,11 @@
       <c r="C15">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -4460,6 +5659,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UsuarioM\Downloads\big_data\bloques\matematicas\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72E596-1F4E-4C05-98C4-D6DAD5B88FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B32BBA-72D3-4524-B7D8-39C2902287DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="164">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -525,6 +525,15 @@
   </si>
   <si>
     <t>vende el grueso de sus productos con un margen de beneficios pequeño. Entre unos 20 y 30 euros de beneficio.</t>
+  </si>
+  <si>
+    <t>la mediana y ka medida son muy parecidas, no hasy dispersion y los valores son muy repetidos</t>
+  </si>
+  <si>
+    <t>la moda es la valoracion mas repetida</t>
+  </si>
+  <si>
+    <t>para ver que puntuacion es mas elevada</t>
   </si>
 </sst>
 </file>
@@ -1236,6 +1245,387 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Distribución de satisfacción</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'3_Satisfaccion'!$E$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nº de Clientes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-ES"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'3_Satisfaccion'!$D$12:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'3_Satisfaccion'!$E$12:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CD63-441B-9353-C4DE129FB79F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="135685039"/>
+        <c:axId val="135684559"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="135685039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="135684559"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="135684559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="95000"/>
+                      <a:lumOff val="5000"/>
+                      <a:alpha val="42000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                      <a:alpha val="36000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="135685039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1359,6 +1749,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -2379,6 +2809,576 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2487,6 +3487,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{311C651B-C93D-291E-D181-64AE538CE65D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1036320</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1440180</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02653E75-52EA-444F-E906-2ED4D6B3B7E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5665,21 +6706,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="81.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -5693,7 +6735,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -5703,9 +6745,12 @@
       <c r="D5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E5" s="4">
+        <f>AVERAGE(B:B)</f>
+        <v>4.2857142857142856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -5715,9 +6760,15 @@
       <c r="D6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6" s="4">
+        <f>MEDIAN(B:B)</f>
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -5727,9 +6778,15 @@
       <c r="D7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" s="4">
+        <f>_xlfn.MODE.SNGL(B:B)</f>
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -5737,7 +6794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -5745,7 +6802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -5756,7 +6813,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -5770,7 +6827,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -5780,9 +6837,12 @@
       <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12" s="4">
+        <f>COUNTIF($B$5:$B$46,D12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5792,9 +6852,12 @@
       <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E13" s="4">
+        <f t="shared" ref="E13:E16" si="0">COUNTIF($B$5:$B$46,D13)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -5804,9 +6867,12 @@
       <c r="D14" s="3">
         <v>3</v>
       </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -5816,9 +6882,12 @@
       <c r="D15" s="3">
         <v>4</v>
       </c>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -5828,9 +6897,12 @@
       <c r="D16" s="3">
         <v>5</v>
       </c>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -5838,7 +6910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -5846,7 +6918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -5857,15 +6929,18 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
       <c r="B20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -5873,7 +6948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -5881,7 +6956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -5889,7 +6964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -5897,7 +6972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -5905,7 +6980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -5913,7 +6988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -5921,7 +6996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -5929,7 +7004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -5937,7 +7012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -5945,7 +7020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -5953,7 +7028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -6075,6 +7150,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UsuarioM\Downloads\big_data\bloques\matematicas\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B32BBA-72D3-4524-B7D8-39C2902287DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C5D51A-DBCC-4850-93CB-54608D167EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="166">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -534,6 +534,12 @@
   </si>
   <si>
     <t>para ver que puntuacion es mas elevada</t>
+  </si>
+  <si>
+    <t>la formula es CONTAR.SI porque tiene el formato condicional del canal de venta</t>
+  </si>
+  <si>
+    <t>hay que tener en cuenta el simbolo $ para filas y columnas en la celda en el calculo de las fórmulas.</t>
   </si>
 </sst>
 </file>
@@ -1626,6 +1632,438 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Probabilidad/Ventas por canal</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-ES"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="95000"/>
+                      <a:alpha val="54000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4_Probabilidad'!$D$6:$D$8</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>App</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Web</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tienda</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4_Probabilidad'!$E$6:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9068-4F0D-9276-7E70FE959898}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1789,6 +2227,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -3378,6 +3856,502 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="257">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -3528,6 +4502,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02653E75-52EA-444F-E906-2ED4D6B3B7E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>140970</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4594860</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>140970</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BEFE71E-C867-F1F0-8B96-56C7F78CC1F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7156,26 +8171,31 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98BB36B-BB56-6748-8634-193EA745B178}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="4" width="15.6640625" customWidth="1"/>
+    <col min="2" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="77.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="20.6640625" customWidth="1"/>
+    <col min="9" max="9" width="87.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E3" s="4">
+        <f>COUNTA(A5:A46)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -7183,7 +8203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -7203,7 +8223,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -7213,11 +8233,23 @@
       <c r="D6" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E6" s="4">
+        <f>COUNTIF(B5:B46,D6)</f>
+        <v>11</v>
+      </c>
+      <c r="F6" s="8">
+        <f>E6/$E$3</f>
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="G6" s="7">
+        <f>F6</f>
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="I6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -7227,11 +8259,23 @@
       <c r="D7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E7" s="4">
+        <f t="shared" ref="E7:E8" si="0">COUNTIF(B6:B47,D7)</f>
+        <v>17</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" ref="F7:F8" si="1">E7/$E$3</f>
+        <v>0.40476190476190477</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" ref="G7:G8" si="2">F7</f>
+        <v>0.40476190476190477</v>
+      </c>
+      <c r="I7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -7241,11 +8285,20 @@
       <c r="D8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -7255,11 +8308,20 @@
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E9" s="4">
+        <f>SUM(E6:E8)</f>
+        <v>42</v>
+      </c>
+      <c r="F9" s="8">
+        <f>SUM(F6:F8)</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <f>SUM(G6:G8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -7267,7 +8329,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -7278,7 +8340,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -7289,7 +8351,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -7300,7 +8362,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -7308,7 +8370,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -7319,7 +8381,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -7572,5 +8634,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>